--- a/강의예제/7장_기본과_필수_함수_익히기/7장_종합문제.xlsx
+++ b/강의예제/7장_기본과_필수_함수_익히기/7장_종합문제.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,15 +130,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -146,6 +149,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -630,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O13"/>
+  <dimension ref="B1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -642,12 +648,13 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,10 +675,8 @@
           <t>기준일</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
+      <c r="F3" s="6" t="n">
+        <v>46281</v>
       </c>
     </row>
     <row r="5">
@@ -715,22 +720,27 @@
           <t>진짜 날짜</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>경과 개월</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>제품코드</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>거래처</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -742,37 +752,38 @@
           <t xml:space="preserve">　　　한결상사</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>260115</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>FQ-003</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="L6" s="14" t="n">
+        <v>8500</v>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>FQ-003</t>
         </is>
       </c>
-      <c r="L6" s="12" t="n">
-        <v>8500</v>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>대성물산</t>
         </is>
       </c>
-      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="8" t="inlineStr">
@@ -780,37 +791,38 @@
           <t>미래산업</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>260228</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>JD-005</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="L7" s="14" t="n">
+        <v>12400</v>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>JD-005</t>
         </is>
       </c>
-      <c r="L7" s="12" t="n">
-        <v>12400</v>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>미래산업</t>
         </is>
       </c>
-      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
@@ -818,37 +830,38 @@
           <t xml:space="preserve">　　　대성물산</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>260310</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>KM-011</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="L8" s="14" t="n">
+        <v>6300</v>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>KM-011</t>
         </is>
       </c>
-      <c r="L8" s="12" t="n">
-        <v>6300</v>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>신영테크</t>
         </is>
       </c>
-      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
@@ -856,37 +869,38 @@
           <t>신영테크</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>260402</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>PL-027</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="L9" s="14" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>PL-027</t>
         </is>
       </c>
-      <c r="L9" s="12" t="n">
-        <v>21000</v>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>한결상사</t>
         </is>
       </c>
-      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="8" t="inlineStr">
@@ -894,30 +908,31 @@
           <t xml:space="preserve">　　　한결상사</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>260519</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>SY-040</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="L10" s="14" t="n">
+        <v>4800</v>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>SY-040</t>
         </is>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>4800</v>
       </c>
     </row>
     <row r="11">
@@ -926,23 +941,24 @@
           <t>미래산업</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>260620</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>FQ-003</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="11" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
@@ -950,23 +966,24 @@
           <t xml:space="preserve">　　　대성물산</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>260711</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>JD-005</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="8" t="inlineStr">
@@ -974,23 +991,24 @@
           <t>신영테크</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>260805</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>KM-011</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="11" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1012,7 +1030,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>최종확인</t>
         </is>
@@ -1038,44 +1056,44 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>① 공백이 안 붙은 거래처 줄은 몇 줄?</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n"/>
+      <c r="C5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>② 금액 합계는?</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n"/>
+      <c r="C6" s="18" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>③ 가장 많이 산 거래처는?</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
+      <c r="C7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>④ 기준일까지 6개월 이상 지난 건은?</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n"/>
+      <c r="C8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>⑤ 공백이 붙은 거래처명의 LEN 값은?</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n"/>
+      <c r="C9" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -1106,7 +1124,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>정답</t>
         </is>
@@ -1142,176 +1160,183 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>글자 수</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>7-07</t>
         </is>
       </c>
-      <c r="E5" s="18">
-        <f>LEN(B6). 「한결상사」는 4여야 하는데 7 이 나옵니다. 앞에 공백이 셋 붙어 있습니다.</f>
-        <v/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>빈 칸 아무 데나 =LEN(B6). 「한결상사」는 4여야 하는데 7 이 나옵니다. 앞에 공백이 셋 붙어 있습니다.</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>공백 떼기</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>7-07</t>
         </is>
       </c>
-      <c r="E6" s="18">
-        <f>TRIM(B6). 웹에서 온 자료라면 =TRIM(SUBSTITUTE(B6,CHAR(160)," ")) 가 안전합니다.</f>
-        <v/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>H6 = TRIM(B6) 을 H13 까지. 웹에서 온 자료라면 =TRIM(SUBSTITUTE(B6,CHAR(160)," ")) 가 안전합니다.</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>7-11</t>
         </is>
       </c>
-      <c r="E7" s="18">
-        <f>DATE(LEFT(C6,2)+2000,MID(C6,3,2),RIGHT(C6,2)). +2000 을 빼먹으면 서기 26년이 됩니다.</f>
-        <v/>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>I6 = DATE(LEFT(C6,2)+2000,MID(C6,3,2),RIGHT(C6,2)). +2000 을 빼먹으면 서기 26년이 됩니다.</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>7-20</t>
         </is>
       </c>
-      <c r="E8" s="18">
-        <f>INDEX($L$6:$L$10,MATCH(D6,$K$6:$K$10,0)). 찾을 열이 오른쪽이라 VLOOKUP 은 안 됩니다.</f>
-        <v/>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>F6 = INDEX($L$6:$L$10,MATCH(D6,$M$6:$M$10,0)). 찾을 열(M 제품코드)이 단가(L)보다 오른쪽이라 VLOOKUP 은 안 됩니다.</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>⑤</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>7-01</t>
         </is>
       </c>
-      <c r="E9" s="18">
-        <f>E6*F6.</f>
-        <v/>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>G6 = E6*F6.</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>거래처별 합계</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>7-05</t>
         </is>
       </c>
-      <c r="E10" s="18">
-        <f>SUMIFS($G$6:$G$13,$H$6:$H$13,J6) — 원본 B열이 아니라 TRIM 한 H열을 봐야 합니다.</f>
-        <v/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>P6 = SUMIFS($G$6:$G$13,$H$6:$H$13,O6) 을 P9 까지. 원본 B열이 아니라 TRIM 한 H열을 봐야 합니다.</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>⑦</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>경과 개월</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>7-12</t>
         </is>
       </c>
-      <c r="E11" s="18">
-        <f>DATEDIF(I6,$F$3,"M"). 자동 완성에 안 뜨니 손으로 전부 치세요.</f>
-        <v/>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>J6 = DATEDIF(I6,$F$3,"M") 을 J13 까지. 자동 완성에 안 뜨니 손으로 전부 치세요.</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>⑧</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>최종확인</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>[최종확인] 주황 칸 다섯 개를 채웁니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>최종확인 답</t>
         </is>
@@ -1336,39 +1361,39 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>②를 하기 전에 SUMIFS 를 걸면 이 4줄만 잡힙니다. 나머지 4줄이 조용히 빠집니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="23" t="n">
         <v>2587500</v>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>④·⑤를 다 해야 나옵니다. 단가를 못 찾은 줄이 있으면 작아집니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1378,40 +1403,40 @@
           <t>한결상사</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>⑥의 SUMIFS 결과를 견주면 됩니다. TRIM 을 안 하면 답이 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>③·⑦을 다 해야 셉니다. 기준일은 F3 에 적혀 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>「한결상사」 4글자 + 앞 공백 3개 = 7. 눈으로는 절대 안 보입니다.</t>
         </is>
